--- a/grafico.xlsx
+++ b/grafico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98A3B096-FDE9-42F7-8AF4-E5E4003DBB69}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{460F38C9-587B-4A08-A26F-1FA3B09473C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{40B6D7D4-34EB-4AB9-9E95-68331FFCF9B3}"/>
   </bookViews>
@@ -86,13 +86,13 @@
     <t>THREADS</t>
   </si>
   <si>
-    <t>TEMPO</t>
-  </si>
-  <si>
     <t>SPEEDUP</t>
   </si>
   <si>
     <t>EFICIÊNCIA</t>
+  </si>
+  <si>
+    <t>TEMPO(s)</t>
   </si>
 </sst>
 </file>
@@ -263,16 +263,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.83333333333333337</c:v>
+                  <c:v>0.82380952380952377</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.83333333333333337</c:v>
+                  <c:v>0.67578125</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.625</c:v>
+                  <c:v>0.59246575342465757</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.55555555555555558</c:v>
+                  <c:v>0.565359477124183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -534,16 +534,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.6666666666666667</c:v>
+                  <c:v>1.6476190476190475</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.3333333333333335</c:v>
+                  <c:v>2.703125</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-">
-                  <c:v>5</c:v>
+                  <c:v>4.7397260273972606</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.666666666666667</c:v>
+                  <c:v>6.784313725490196</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2218,13 +2218,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>346</v>
       </c>
       <c r="C2">
         <f>B2/B2</f>
@@ -2248,15 +2248,15 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="C3" s="3">
         <f>B2/B3</f>
-        <v>1.6666666666666667</v>
+        <v>1.6476190476190475</v>
       </c>
       <c r="D3" s="2">
         <f>C3/A3</f>
-        <v>0.83333333333333337</v>
+        <v>0.82380952380952377</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -2265,15 +2265,15 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="C4" s="3">
         <f>B2/B4</f>
-        <v>3.3333333333333335</v>
+        <v>2.703125</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" ref="D4:D6" si="0">C4/A4</f>
-        <v>0.83333333333333337</v>
+        <v>0.67578125</v>
       </c>
       <c r="E4" s="1"/>
     </row>
@@ -2282,15 +2282,15 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4">
         <f>B2/B5</f>
-        <v>5</v>
+        <v>4.7397260273972606</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="0"/>
-        <v>0.625</v>
+        <v>0.59246575342465757</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -2299,15 +2299,15 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3">
         <f>B2/B6</f>
-        <v>6.666666666666667</v>
+        <v>6.784313725490196</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
-        <v>0.55555555555555558</v>
+        <v>0.565359477124183</v>
       </c>
       <c r="E6" s="1"/>
     </row>
